--- a/scraper/uni_list.xlsx
+++ b/scraper/uni_list.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -42,11 +42,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,10 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -625,2745 +619,2447 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>12542</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>University of Zurich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Department of Business Administration</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Postdoc in Economics of Education and Labor Economics</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Postdoc</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Labor; Demographic Economics | Health; Education; Welfare | Business Economics | Applied microeconomics</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" t="n">
         <v>61</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>3 years</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Cover letter, CV, Writing/research sample</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12542</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>12598</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>CEMFI</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>All departments</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-H Research Project Coordinator</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Researcher (Non-academic)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Labor; Demographic Economics | Public Economics | Political Economy | Applied microeconomics</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" t="n">
         <v>24</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2 years</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Masters</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Cover letter, CV, Research statement, Writing/research sample</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12598</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>12539</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>UniDistance</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>All departments</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Assistant Professorships in Empirical Management Research</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Industrial Organization | Business Economics | Accounting | Decision Sciences | Management, General | Management, Information Technology | Marketing | Operations Research | Organizational Behavior</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Wallis</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>CV, Research statement, Teaching statement, Publication list</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12539</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>12537</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>University of Fribourg</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Professorship in Applied Microeconomics (Open Rank)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Applied microeconomics</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" t="n">
         <v>26</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Fribourg</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2027-08-01</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Cover letter, CV, Teaching statement, Publication list</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12537</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr"/>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>12551</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>University of Oxford</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Nuffield Postdoctoral Research Fellowships</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Postdoc</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Any field</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>OX 1 3UQ</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2027-09-01</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>3 years</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12551</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr"/>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr"/>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>12608</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Ghent University</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Professor in International Economics</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Industrial Organization | International Trade</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Gent</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>2027-02-01</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>5 years</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>CV, Transcripts, Publication list</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12608</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr"/>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>12543</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>University of Oxford</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Postdoctoral Research Fellow</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Postdoc</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Any field</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>OX 1 3UQ</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>1 year</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12543</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr"/>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>12555</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Université Paris-Dauphine</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>LEDa (Laboratoire d’Economie de Dauphine)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Junior Professor Chair in Economics, Information, Data &amp; AI, Paris, France</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Any field</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" t="n">
         <v>21</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Transcripts</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12555</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr"/>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr"/>
-      <c r="Y9" s="2" t="inlineStr"/>
-      <c r="Z9" s="2" t="inlineStr"/>
-      <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>12599</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>EJM + EJME</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Maynooth University</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Assistant Professor, Macroeconomics</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Macroeconomics; Monetary</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Co. Kildare</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Cover letter, CV, Research statement</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12599</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr"/>
-      <c r="Z10" s="2" t="inlineStr"/>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>12561</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Bocconi University</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Two Assistant Professor Positions in Economics for Experienced Candidates</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Any field</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" t="n">
         <v>9</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Milano</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>2027-09-01</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>6 years</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12561</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr"/>
-      <c r="V11" s="2" t="inlineStr"/>
-      <c r="W11" s="2" t="inlineStr"/>
-      <c r="X11" s="2" t="inlineStr"/>
-      <c r="Y11" s="2" t="inlineStr"/>
-      <c r="Z11" s="2" t="inlineStr"/>
-      <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>12530</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Norwegian University of Science and Technology</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Business School</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Postdoctoral Fellow in Business and Administration</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Postdoc</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Econometrics | Finance | Labor; Demographic Economics | Public Economics | Behavioral Economics | Urban; Rural; Regional Economics | Accounting | Real Estate | Applied microeconomics</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" t="n">
         <v>27</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Trondheim</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>3 years</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>CV, Research statement, Transcripts, Publication list</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12530</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr"/>
-      <c r="V12" s="2" t="inlineStr"/>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="2" t="inlineStr"/>
-      <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="2" t="inlineStr"/>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>12513</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Institut Polytechnique de Paris</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Post-doctoral position in Experimental Economics</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Postdoc</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Experimental Economics</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" t="n">
         <v>12</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Palaiseau</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Interviews will be conducted remotely by video</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>24 months</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12513</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
-      <c r="V13" s="2" t="inlineStr"/>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="inlineStr"/>
-      <c r="Y13" s="2" t="inlineStr"/>
-      <c r="Z13" s="2" t="inlineStr"/>
-      <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>12514</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Institut Polytechnique de Paris</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Lab Manager in Experimental Economics</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Researcher (Other academic)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Experimental Economics</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Palaiseau</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Interviews will be conducted remotely by video</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>36 months</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper, Writing/research sample</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12514</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr"/>
-      <c r="V14" s="2" t="inlineStr"/>
-      <c r="W14" s="2" t="inlineStr"/>
-      <c r="X14" s="2" t="inlineStr"/>
-      <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr"/>
-      <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>12569</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>OECD (Organisation for Economic Co-operation and Development)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Economics Department</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Junior Economists/ Economists</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Researcher (Other academic)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Econometrics | International Finance/Macro | International Trade | Labor; Demographic Economics | Macroeconomics; Monetary | Public Economics | Business Economics | Political Economy | Applied microeconomics</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" t="n">
         <v>22</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2026-11-01</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Interviews will be conducted remotely by video</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>2027-09-01</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>2 years</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12569</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr"/>
-      <c r="V15" s="2" t="inlineStr"/>
-      <c r="W15" s="2" t="inlineStr"/>
-      <c r="X15" s="2" t="inlineStr"/>
-      <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr"/>
-      <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD15" s="2" t="inlineStr">
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>12552</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>University of Bonn</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Institut für Makroökonomik und Ökonometrie</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Two postdoctoral researcher positions (E13 TV-L, full-time)</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Postdoc</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>International Finance/Macro | International Trade | Labor; Demographic Economics | Macroeconomics; Monetary</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" t="n">
         <v>27</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>NRW</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2026-11-15</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Interviews will be conducted remotely by video</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>2027-09-01</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>3 years</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper, Writing/research sample</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12552</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr"/>
-      <c r="V16" s="2" t="inlineStr"/>
-      <c r="W16" s="2" t="inlineStr"/>
-      <c r="X16" s="2" t="inlineStr"/>
-      <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="2" t="inlineStr"/>
-      <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="inlineStr">
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>12593</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>EJM + EJME</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>University of Bonn</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Two Assistant Professorships in Econometrics (W1 with Tenure Track to W2)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Econometrics</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Bonn</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2026-11-15</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper, Research statement</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12593</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr"/>
-      <c r="V17" s="2" t="inlineStr"/>
-      <c r="W17" s="2" t="inlineStr"/>
-      <c r="X17" s="2" t="inlineStr"/>
-      <c r="Y17" s="2" t="inlineStr"/>
-      <c r="Z17" s="2" t="inlineStr"/>
-      <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="inlineStr">
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>12594</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>EJM + EJME</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>University of Bonn</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Assistant Professorship in Finance (W1 with Tenure Track to W2)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Bonn</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper, Research statement</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12594</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr"/>
-      <c r="V18" s="2" t="inlineStr"/>
-      <c r="W18" s="2" t="inlineStr"/>
-      <c r="X18" s="2" t="inlineStr"/>
-      <c r="Y18" s="2" t="inlineStr"/>
-      <c r="Z18" s="2" t="inlineStr"/>
-      <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD18" s="2" t="inlineStr">
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>12586</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>EJM + EJME</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Halle Institute for Economic Research (IWH)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>All departments</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Assistant Professor (W1) in Financial Economics</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Finance | Labor; Demographic Economics</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" t="n">
         <v>17</v>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-11-29</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>2027-10-01</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>6 years</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper, Research statement, Teaching statement, Publication list</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12586</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr"/>
-      <c r="V19" s="2" t="inlineStr"/>
-      <c r="W19" s="2" t="inlineStr"/>
-      <c r="X19" s="2" t="inlineStr"/>
-      <c r="Y19" s="2" t="inlineStr"/>
-      <c r="Z19" s="2" t="inlineStr"/>
-      <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="inlineStr">
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>12205</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Plaksha University</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>All departments</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Faculty of Economics at Plaksha University, India</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Econometrics | Finance | International Finance/Macro | Labor; Demographic Economics | Macroeconomics; Monetary | Any field | Business Economics | Computational Economics | Marketing | Operations Research | Real Estate | Statistics | Microeconomic theory | Applied microeconomics</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" t="n">
         <v>20</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2026-12-01</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12205</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
-      <c r="V20" s="2" t="inlineStr"/>
-      <c r="W20" s="2" t="inlineStr"/>
-      <c r="X20" s="2" t="inlineStr"/>
-      <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr"/>
-      <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD20" s="2" t="inlineStr">
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>12225</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Indian Institute of Science Education and Research Bhopal</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Department of Economic Sciences</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Assistant Professor / Associate Professor / Professor /</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Any field</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I21" t="n">
         <v>6</v>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>2026-12-05</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12225</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
-      <c r="V21" s="2" t="inlineStr"/>
-      <c r="W21" s="2" t="inlineStr"/>
-      <c r="X21" s="2" t="inlineStr"/>
-      <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="2" t="inlineStr"/>
-      <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>12485</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>CY Cergy Paris Université</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>THEMA (Theorie Economique, Modelisation et Applications)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Postdoctoral Researcher (3 Years) – Transport / Urban Economics / Data Science</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Postdoc</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Econometrics | Environmental; Ag. Econ. | Public Economics | Behavioral Economics | Any field | Urban; Rural; Regional Economics | Applied microeconomics</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" t="n">
         <v>20</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Cergy-Pontoise</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Interviews will be conducted remotely by video</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Flexible</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>3 years</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12485</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
-      <c r="V22" s="2" t="inlineStr"/>
-      <c r="W22" s="2" t="inlineStr"/>
-      <c r="X22" s="2" t="inlineStr"/>
-      <c r="Y22" s="2" t="inlineStr"/>
-      <c r="Z22" s="2" t="inlineStr"/>
-      <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD22" s="2" t="inlineStr">
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>12554</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Simon Fraser University</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Department of Economics</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Assistant/Associate Professor</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Econometrics | Environmental; Ag. Econ. | Industrial Organization | International Trade | Urban; Rural; Regional Economics</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I23" t="n">
         <v>7</v>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>CHECK: "eligible to work in"</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>2027-07-01</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper, Research statement, Teaching statement, Writing/research sample</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12554</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
-      <c r="V23" s="2" t="inlineStr"/>
-      <c r="W23" s="2" t="inlineStr"/>
-      <c r="X23" s="2" t="inlineStr"/>
-      <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr"/>
-      <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC23" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD23" s="2" t="inlineStr">
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>12602</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>EJM</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>University of Toronto</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Assistant Professor, Teaching Stream - Macroeconomics</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Macroeconomics; Monetary</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" t="n">
         <v>6</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>No restriction found</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>2027-04-30</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Interviews will be conducted remotely by video</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>2027-07-01</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Continuing/permanent</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Cover letter, CV, Job market paper, Teaching statement, Diversity statement</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>https://econjobmarket.org/positions/12602</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
-      <c r="V24" s="2" t="inlineStr"/>
-      <c r="W24" s="2" t="inlineStr"/>
-      <c r="X24" s="2" t="inlineStr"/>
-      <c r="Y24" s="2" t="inlineStr"/>
-      <c r="Z24" s="2" t="inlineStr"/>
-      <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AD24" s="2" t="inlineStr">
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="AE24" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE24"/>
